--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V228"/>
+  <dimension ref="A1:V230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22839,6 +22842,210 @@
       <c r="V228" t="inlineStr">
         <is>
           <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>90793</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>48</v>
+      </c>
+      <c r="J229" t="n">
+        <v>4</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>13364000</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>40429</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>90903</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN PÚBLICA Y GOBIERNO</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>60</v>
+      </c>
+      <c r="J230" t="n">
+        <v>4</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>13883700</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>43185</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V230"/>
+  <dimension ref="A1:V234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22846,10 +22846,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A229" t="n">
+        <v>1830</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -22903,7 +22901,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N229" s="2" t="n">
+      <c r="N229" s="1" t="n">
         <v>40429</v>
       </c>
       <c r="O229" t="inlineStr">
@@ -22948,10 +22946,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A230" t="n">
+        <v>2832</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -23005,7 +23001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N230" s="2" t="n">
+      <c r="N230" s="1" t="n">
         <v>43185</v>
       </c>
       <c r="O230" t="inlineStr">
@@ -23046,6 +23042,408 @@
       <c r="V230" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>52398</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN REDES</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>21</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>38995</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>101308</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MODELACIÓN Y CIENCIA COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>48</v>
+      </c>
+      <c r="J232" t="n">
+        <v>4</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>9896428</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>43529</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CES</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>5086</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN CIRUGIA PLASTICA FACIAL</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>62</v>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CAFAM -UNICAFAM</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>105332</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>27</v>
+      </c>
+      <c r="J234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>42416</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V234"/>
+  <dimension ref="A1:V241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23046,10 +23046,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A231" t="n">
+        <v>1722</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -23101,7 +23099,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N231" s="2" t="n">
+      <c r="N231" s="1" t="n">
         <v>38995</v>
       </c>
       <c r="O231" t="inlineStr">
@@ -23146,10 +23144,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A232" t="n">
+        <v>1812</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -23203,7 +23199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N232" s="2" t="n">
+      <c r="N232" s="1" t="n">
         <v>43529</v>
       </c>
       <c r="O232" t="inlineStr">
@@ -23248,10 +23244,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="A233" t="n">
+        <v>2708</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -23303,7 +23297,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N233" s="2" t="n">
+      <c r="N233" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O233" t="inlineStr">
@@ -23348,10 +23342,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>9129</t>
-        </is>
+      <c r="A234" t="n">
+        <v>9129</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -23403,7 +23395,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N234" s="2" t="n">
+      <c r="N234" s="1" t="n">
         <v>42416</v>
       </c>
       <c r="O234" t="inlineStr">
@@ -23442,6 +23434,712 @@
         </is>
       </c>
       <c r="V234" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Santander de Quilichao</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>106198</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOINGENIERÍA</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>42</v>
+      </c>
+      <c r="J235" t="n">
+        <v>2</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LLANOS</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>90787</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PRODUCCIÓN TROPICAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>54</v>
+      </c>
+      <c r="J236" t="n">
+        <v>2</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>7598928</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>40429</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Agronomía</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EXTERNADO DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>15900</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ADMINISTRACION DE RIESGOS INFORMATICOS</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>28</v>
+      </c>
+      <c r="J237" t="n">
+        <v>2</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>12376000</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>43278</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Uso de computadores</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>104806</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ESCRITURAS CREATIVAS</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>36</v>
+      </c>
+      <c r="J238" t="n">
+        <v>3</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>42224</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Artesanías</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>54790</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN HERMENÈUTICA LITERARIA</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>36</v>
+      </c>
+      <c r="J239" t="n">
+        <v>4</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>40043</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Literatura y lingüística</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>90475</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE REDES TELEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>32</v>
+      </c>
+      <c r="J240" t="n">
+        <v>2</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>7790000</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>42758</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>107187</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PROSPECTIVA TECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>26</v>
+      </c>
+      <c r="J241" t="n">
+        <v>2</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>43296</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
         <is>
           <t>Ingenierías</t>
         </is>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V241"/>
+  <dimension ref="A1:V243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23440,10 +23440,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A235" t="n">
+        <v>1110</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -23495,7 +23493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N235" s="2" t="n">
+      <c r="N235" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O235" t="inlineStr">
@@ -23540,10 +23538,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
+      <c r="A236" t="n">
+        <v>1119</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -23597,7 +23593,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N236" s="2" t="n">
+      <c r="N236" s="1" t="n">
         <v>40429</v>
       </c>
       <c r="O236" t="inlineStr">
@@ -23642,10 +23638,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A237" t="n">
+        <v>1706</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -23699,7 +23693,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N237" s="2" t="n">
+      <c r="N237" s="1" t="n">
         <v>43278</v>
       </c>
       <c r="O237" t="inlineStr">
@@ -23744,10 +23738,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A238" t="n">
+        <v>1712</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -23799,7 +23791,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N238" s="2" t="n">
+      <c r="N238" s="1" t="n">
         <v>42224</v>
       </c>
       <c r="O238" t="inlineStr">
@@ -23844,10 +23836,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A239" t="n">
+        <v>1712</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -23899,7 +23889,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N239" s="2" t="n">
+      <c r="N239" s="1" t="n">
         <v>40043</v>
       </c>
       <c r="O239" t="inlineStr">
@@ -23944,10 +23934,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A240" t="n">
+        <v>1729</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -24001,7 +23989,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N240" s="2" t="n">
+      <c r="N240" s="1" t="n">
         <v>42758</v>
       </c>
       <c r="O240" t="inlineStr">
@@ -24046,10 +24034,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A241" t="n">
+        <v>2302</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -24101,7 +24087,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N241" s="2" t="n">
+      <c r="N241" s="1" t="n">
         <v>43296</v>
       </c>
       <c r="O241" t="inlineStr">
@@ -24142,6 +24128,208 @@
       <c r="V241" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>102255</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DIDÁCTICA DE LA LENGUA</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>51</v>
+      </c>
+      <c r="J242" t="n">
+        <v>4</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>9872684</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>43623</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>106589</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>50</v>
+      </c>
+      <c r="J243" t="n">
+        <v>4</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>43077</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V243"/>
+  <dimension ref="A1:V245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24132,10 +24132,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A242" t="n">
+        <v>1204</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -24189,7 +24187,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N242" s="2" t="n">
+      <c r="N242" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="O242" t="inlineStr">
@@ -24234,10 +24232,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A243" t="n">
+        <v>1722</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -24289,7 +24285,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N243" s="2" t="n">
+      <c r="N243" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="O243" t="inlineStr">
@@ -24330,6 +24326,208 @@
       <c r="V243" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>102587</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN FILOSOFIA</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>40</v>
+      </c>
+      <c r="J244" t="n">
+        <v>4</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>11173938</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>43826</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Filosofía y ética</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>106750</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENSEÑANZA Y APRENDIZAJE DEL INGLÉS</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>47</v>
+      </c>
+      <c r="J245" t="n">
+        <v>4</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>43180</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V245"/>
+  <dimension ref="A1:V248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24330,10 +24330,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A244" t="n">
+        <v>1713</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -24387,7 +24385,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N244" s="2" t="n">
+      <c r="N244" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="O244" t="inlineStr">
@@ -24432,10 +24430,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A245" t="n">
+        <v>1805</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -24487,7 +24483,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N245" s="2" t="n">
+      <c r="N245" s="1" t="n">
         <v>43180</v>
       </c>
       <c r="O245" t="inlineStr">
@@ -24528,6 +24524,310 @@
       <c r="V245" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>107750</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN COMUNICACIÓN POLÍTICA</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>36</v>
+      </c>
+      <c r="J246" t="n">
+        <v>3</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>13692443</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>43495</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>107549</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>26</v>
+      </c>
+      <c r="J247" t="n">
+        <v>2</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>43449</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>107405</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ADMINISTRACIÓN DE SISTEMAS TELEMÁTICOS</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>30</v>
+      </c>
+      <c r="J248" t="n">
+        <v>2</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>7105173</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>45623</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V248"/>
+  <dimension ref="A1:V253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24528,10 +24528,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A246" t="n">
+        <v>1712</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -24585,7 +24583,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N246" s="2" t="n">
+      <c r="N246" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O246" t="inlineStr">
@@ -24630,10 +24628,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A247" t="n">
+        <v>2302</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -24685,7 +24681,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N247" s="2" t="n">
+      <c r="N247" s="1" t="n">
         <v>43449</v>
       </c>
       <c r="O247" t="inlineStr">
@@ -24730,10 +24726,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A248" t="n">
+        <v>3117</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -24787,7 +24781,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N248" s="2" t="n">
+      <c r="N248" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O248" t="inlineStr">
@@ -24828,6 +24822,514 @@
       <c r="V248" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>654</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENFERMERÍA CON ÉNFASIS EN CUIDADO MATERNO -INFANTIL, CUIDADO AL ADULTO Y AL ANCIANO, Y CUIDADO AL NIÑO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>36</v>
+      </c>
+      <c r="J249" t="n">
+        <v>5</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>665675</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>43719</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Buenaventura</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>118340</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PORTUARIA Y MARÍTIMA</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>23</v>
+      </c>
+      <c r="J250" t="n">
+        <v>2</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>107048</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA COMUNICACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>22</v>
+      </c>
+      <c r="J251" t="n">
+        <v>2</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>9212700</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>43282</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>105869</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN PARA LOS DERECHOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>56</v>
+      </c>
+      <c r="J252" t="n">
+        <v>2</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>16096350</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>42653</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>12286</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN INFORMATICA EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>26</v>
+      </c>
+      <c r="J253" t="n">
+        <v>2</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>4610306</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>37089</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V253"/>
+  <dimension ref="A1:V258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24826,10 +24826,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A249" t="n">
+        <v>1203</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -24883,7 +24881,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N249" s="2" t="n">
+      <c r="N249" s="1" t="n">
         <v>43719</v>
       </c>
       <c r="O249" t="inlineStr">
@@ -24928,10 +24926,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A250" t="n">
+        <v>1716</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -24983,7 +24979,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N250" s="2" t="n">
+      <c r="N250" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O250" t="inlineStr">
@@ -25028,10 +25024,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A251" t="n">
+        <v>1722</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -25085,7 +25079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N251" s="2" t="n">
+      <c r="N251" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="O251" t="inlineStr">
@@ -25130,10 +25124,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A252" t="n">
+        <v>1728</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -25187,7 +25179,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N252" s="2" t="n">
+      <c r="N252" s="1" t="n">
         <v>42653</v>
       </c>
       <c r="O252" t="inlineStr">
@@ -25232,10 +25224,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A253" t="n">
+        <v>2731</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -25289,7 +25279,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N253" s="2" t="n">
+      <c r="N253" s="1" t="n">
         <v>37089</v>
       </c>
       <c r="O253" t="inlineStr">
@@ -25330,6 +25320,514 @@
       <c r="V253" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>10148</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DESARROLLO PERSONAL Y FAMILIAR</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>25</v>
+      </c>
+      <c r="J254" t="n">
+        <v>2</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>19843</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN PSICOLOGIA</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>40</v>
+      </c>
+      <c r="J255" t="n">
+        <v>4</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>16640849</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>44545</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>108238</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTERNET DE LAS COSAS Y CONTROL</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>51</v>
+      </c>
+      <c r="J256" t="n">
+        <v>4</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
+        <v>11547000</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>43705</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>117428</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN DIRECCION Y GESTION TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>43</v>
+      </c>
+      <c r="J257" t="n">
+        <v>4</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>20765600</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DIRECCION DE EDUCACION POLICIAL</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>2651</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>29</v>
+      </c>
+      <c r="J258" t="n">
+        <v>2</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>8993673</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Servicios de seguridad</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Educación militar y de defensa</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Formación relacionada con el campo militar o policial</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Otro</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V258"/>
+  <dimension ref="A1:V266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25324,10 +25324,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A254" t="n">
+        <v>1711</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -25379,7 +25377,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N254" s="2" t="n">
+      <c r="N254" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O254" t="inlineStr">
@@ -25424,10 +25422,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A255" t="n">
+        <v>1713</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -25481,7 +25477,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N255" s="2" t="n">
+      <c r="N255" s="1" t="n">
         <v>44545</v>
       </c>
       <c r="O255" t="inlineStr">
@@ -25526,10 +25522,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
+      <c r="A256" t="n">
+        <v>1718</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -25583,7 +25577,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N256" s="2" t="n">
+      <c r="N256" s="1" t="n">
         <v>43705</v>
       </c>
       <c r="O256" t="inlineStr">
@@ -25628,10 +25622,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A257" t="n">
+        <v>1728</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -25685,7 +25677,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N257" s="2" t="n">
+      <c r="N257" s="1" t="n">
         <v>45190</v>
       </c>
       <c r="O257" t="inlineStr">
@@ -25730,10 +25722,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A258" t="n">
+        <v>2106</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -25787,7 +25777,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N258" s="2" t="n">
+      <c r="N258" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O258" t="inlineStr">
@@ -25828,6 +25818,818 @@
       <c r="V258" t="inlineStr">
         <is>
           <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>104469</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>90</v>
+      </c>
+      <c r="J259" t="n">
+        <v>8</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
+        <v>22390387</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>44419</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>107825</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>48</v>
+      </c>
+      <c r="J260" t="n">
+        <v>4</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>43542</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>106979</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENTORÍA DE OBRAS CIVILES</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>24</v>
+      </c>
+      <c r="J261" t="n">
+        <v>2</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
+        <v>10782856</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>43277</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>108410</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DESARROLLO DE TECNOLOGIAS MOVILES</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>22</v>
+      </c>
+      <c r="J262" t="n">
+        <v>2</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>43755</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Uso de computadores</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>90793</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>48</v>
+      </c>
+      <c r="J263" t="n">
+        <v>4</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>13364000</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>40429</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>104417</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>48</v>
+      </c>
+      <c r="J264" t="n">
+        <v>4</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>45114</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Periodismo e información no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>104870</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PSICOLOGÍA COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>46</v>
+      </c>
+      <c r="J265" t="n">
+        <v>4</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>42242</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>108824</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>47</v>
+      </c>
+      <c r="J266" t="n">
+        <v>4</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>8746146</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V371"/>
+  <dimension ref="A1:V373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36828,10 +36828,8 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A370" t="n">
+        <v>1701</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -36885,7 +36883,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N370" s="2" t="n">
+      <c r="N370" s="1" t="n">
         <v>43691</v>
       </c>
       <c r="O370" t="inlineStr">
@@ -36930,10 +36928,8 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A371" t="n">
+        <v>1713</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -36987,7 +36983,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N371" s="2" t="n">
+      <c r="N371" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O371" t="inlineStr">
@@ -37028,6 +37024,210 @@
       <c r="V371" t="inlineStr">
         <is>
           <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>107864</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTIÓN GERONTOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I372" t="n">
+        <v>26</v>
+      </c>
+      <c r="J372" t="n">
+        <v>2</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L372" t="n">
+        <v>5331500</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>43500</v>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA VISIÓN DE LAS AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>107148</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN REHABILITACIÓN CARDIOPULMONAR</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I373" t="n">
+        <v>36</v>
+      </c>
+      <c r="J373" t="n">
+        <v>3</v>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L373" t="n">
+        <v>11002624</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>43290</v>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V373"/>
+  <dimension ref="A1:V383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37028,10 +37028,8 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
+      <c r="A372" t="n">
+        <v>2732</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -37085,7 +37083,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N372" s="2" t="n">
+      <c r="N372" s="1" t="n">
         <v>43500</v>
       </c>
       <c r="O372" t="inlineStr">
@@ -37130,10 +37128,8 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
+      <c r="A373" t="n">
+        <v>2747</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -37187,7 +37183,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N373" s="2" t="n">
+      <c r="N373" s="1" t="n">
         <v>43290</v>
       </c>
       <c r="O373" t="inlineStr">
@@ -37228,6 +37224,1016 @@
       <c r="V373" t="inlineStr">
         <is>
           <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LLANOS</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>102134</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ACCION MOTRIZ</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I374" t="n">
+        <v>30</v>
+      </c>
+      <c r="J374" t="n">
+        <v>2</v>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N374" s="2" t="n">
+        <v>41271</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>107748</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERIA MECANICA</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>100</v>
+      </c>
+      <c r="J375" t="n">
+        <v>4</v>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L375" t="n">
+        <v>8012643</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>43558</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>106897</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CALIDAD Y GESTIÓN INTEGRAL</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>48</v>
+      </c>
+      <c r="J376" t="n">
+        <v>4</v>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L376" t="n">
+        <v>10798104</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>43244</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>101715</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DE LAS RELACIONES LABORALES</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>27</v>
+      </c>
+      <c r="J377" t="n">
+        <v>2</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L377" t="n">
+        <v>6961500</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>43746</v>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>103009</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CALIDAD Y AUDITORÍA EN SALUD</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>30</v>
+      </c>
+      <c r="J378" t="n">
+        <v>2</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>44204</v>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>109667</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>50</v>
+      </c>
+      <c r="J379" t="n">
+        <v>4</v>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N379" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>108827</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y ASEGURAMIENTO DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>24</v>
+      </c>
+      <c r="J380" t="n">
+        <v>2</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L380" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>110784</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN COMUNICACION ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>25</v>
+      </c>
+      <c r="J381" t="n">
+        <v>2</v>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>20110</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN COMUNICACION ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>25</v>
+      </c>
+      <c r="J382" t="n">
+        <v>2</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L382" t="n">
+        <v>9779900</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>44273</v>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CAFAM -UNICAFAM</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>105338</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EDUCACIÓN MATEMÁTICA PARA BÁSICA PRIMARIA</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>25</v>
+      </c>
+      <c r="J383" t="n">
+        <v>1</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>42417</v>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V383"/>
+  <dimension ref="A1:V385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37228,10 +37228,8 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
+      <c r="A374" t="n">
+        <v>1119</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -37283,7 +37281,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N374" s="2" t="n">
+      <c r="N374" s="1" t="n">
         <v>41271</v>
       </c>
       <c r="O374" t="inlineStr">
@@ -37328,10 +37326,8 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A375" t="n">
+        <v>1203</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -37385,7 +37381,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N375" s="2" t="n">
+      <c r="N375" s="1" t="n">
         <v>43558</v>
       </c>
       <c r="O375" t="inlineStr">
@@ -37430,10 +37426,8 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A376" t="n">
+        <v>1704</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -37487,7 +37481,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N376" s="2" t="n">
+      <c r="N376" s="1" t="n">
         <v>43244</v>
       </c>
       <c r="O376" t="inlineStr">
@@ -37532,10 +37526,8 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A377" t="n">
+        <v>1705</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -37589,7 +37581,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N377" s="2" t="n">
+      <c r="N377" s="1" t="n">
         <v>43746</v>
       </c>
       <c r="O377" t="inlineStr">
@@ -37634,10 +37626,8 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A378" t="n">
+        <v>1713</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -37689,7 +37679,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N378" s="2" t="n">
+      <c r="N378" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="O378" t="inlineStr">
@@ -37734,10 +37724,8 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A379" t="n">
+        <v>1722</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -37789,7 +37777,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N379" s="2" t="n">
+      <c r="N379" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O379" t="inlineStr">
@@ -37834,10 +37822,8 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A380" t="n">
+        <v>1732</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -37891,7 +37877,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N380" s="2" t="n">
+      <c r="N380" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O380" t="inlineStr">
@@ -37936,10 +37922,8 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A381" t="n">
+        <v>1830</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -37991,7 +37975,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N381" s="2" t="n">
+      <c r="N381" s="1" t="n">
         <v>44258</v>
       </c>
       <c r="O381" t="inlineStr">
@@ -38036,10 +38020,8 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A382" t="n">
+        <v>1830</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -38093,7 +38075,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N382" s="2" t="n">
+      <c r="N382" s="1" t="n">
         <v>44273</v>
       </c>
       <c r="O382" t="inlineStr">
@@ -38138,10 +38120,8 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>9129</t>
-        </is>
+      <c r="A383" t="n">
+        <v>9129</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -38193,7 +38173,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N383" s="2" t="n">
+      <c r="N383" s="1" t="n">
         <v>42417</v>
       </c>
       <c r="O383" t="inlineStr">
@@ -38234,6 +38214,210 @@
       <c r="V383" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>105642</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIAS ECONÓMICAS</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>112</v>
+      </c>
+      <c r="J384" t="n">
+        <v>4</v>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L384" t="n">
+        <v>18262000</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>45112</v>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA KONRAD LORENZ</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>107623</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>24</v>
+      </c>
+      <c r="J385" t="n">
+        <v>2</v>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L385" t="n">
+        <v>9226000</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V385"/>
+  <dimension ref="A1:V396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38218,10 +38218,8 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A384" t="n">
+        <v>1702</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -38275,7 +38273,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N384" s="2" t="n">
+      <c r="N384" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="O384" t="inlineStr">
@@ -38320,10 +38318,8 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A385" t="n">
+        <v>2712</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -38377,7 +38373,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N385" s="2" t="n">
+      <c r="N385" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O385" t="inlineStr">
@@ -38418,6 +38414,1122 @@
       <c r="V385" t="inlineStr">
         <is>
           <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>108362</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA, DESARROLLO E INNOVACIÓN EN TIC</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>56</v>
+      </c>
+      <c r="J386" t="n">
+        <v>4</v>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>43734</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>108753</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTABILIDAD FINANCIERA INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>26</v>
+      </c>
+      <c r="J387" t="n">
+        <v>2</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L387" t="n">
+        <v>12504000</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>109198</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA TRIBUTARIA INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>26</v>
+      </c>
+      <c r="J388" t="n">
+        <v>2</v>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L388" t="n">
+        <v>12504000</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>1217</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION GERENCIA DE LA COMUNICACION ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>24</v>
+      </c>
+      <c r="J389" t="n">
+        <v>2</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L389" t="n">
+        <v>12038760</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>43816</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>102585</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN  RESPONSABILIDAD CIVIL Y DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>22</v>
+      </c>
+      <c r="J390" t="n">
+        <v>2</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L390" t="n">
+        <v>14386306</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>52624</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>22</v>
+      </c>
+      <c r="J391" t="n">
+        <v>2</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L391" t="n">
+        <v>13507000</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>1261</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>24</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L392" t="n">
+        <v>14541897</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>102833</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN HISTORIA</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>40</v>
+      </c>
+      <c r="J393" t="n">
+        <v>4</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L393" t="n">
+        <v>12883994</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>44491</v>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>Geografía, historia</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>54649</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MERCADEO</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>60</v>
+      </c>
+      <c r="J394" t="n">
+        <v>4</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>45218</v>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>107252</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE RECURSOS ENERGÉTICOS</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>22</v>
+      </c>
+      <c r="J395" t="n">
+        <v>2</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>43327</v>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>107622</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN FAMILIAS</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>50</v>
+      </c>
+      <c r="J396" t="n">
+        <v>4</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L396" t="n">
+        <v>8603918</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>43511</v>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V396"/>
+  <dimension ref="A1:V400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38418,10 +38418,8 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="A386" t="n">
+        <v>1205</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -38473,7 +38471,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N386" s="2" t="n">
+      <c r="N386" s="1" t="n">
         <v>43734</v>
       </c>
       <c r="O386" t="inlineStr">
@@ -38518,10 +38516,8 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A387" t="n">
+        <v>1208</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -38575,7 +38571,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N387" s="2" t="n">
+      <c r="N387" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O387" t="inlineStr">
@@ -38620,10 +38616,8 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A388" t="n">
+        <v>1208</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -38677,7 +38671,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N388" s="2" t="n">
+      <c r="N388" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O388" t="inlineStr">
@@ -38722,10 +38716,8 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A389" t="n">
+        <v>1710</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -38779,7 +38771,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N389" s="2" t="n">
+      <c r="N389" s="1" t="n">
         <v>43816</v>
       </c>
       <c r="O389" t="inlineStr">
@@ -38824,10 +38816,8 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A390" t="n">
+        <v>1711</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -38881,7 +38871,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N390" s="2" t="n">
+      <c r="N390" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O390" t="inlineStr">
@@ -38926,10 +38916,8 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A391" t="n">
+        <v>1711</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -38983,7 +38971,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N391" s="2" t="n">
+      <c r="N391" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O391" t="inlineStr">
@@ -39028,10 +39016,8 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A392" t="n">
+        <v>1712</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -39085,7 +39071,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N392" s="2" t="n">
+      <c r="N392" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O392" t="inlineStr">
@@ -39130,10 +39116,8 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A393" t="n">
+        <v>1713</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -39187,7 +39171,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N393" s="2" t="n">
+      <c r="N393" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="O393" t="inlineStr">
@@ -39232,10 +39216,8 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A394" t="n">
+        <v>1713</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -39287,7 +39269,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N394" s="2" t="n">
+      <c r="N394" s="1" t="n">
         <v>45218</v>
       </c>
       <c r="O394" t="inlineStr">
@@ -39332,10 +39314,8 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A395" t="n">
+        <v>1823</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -39387,7 +39367,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N395" s="2" t="n">
+      <c r="N395" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O395" t="inlineStr">
@@ -39432,10 +39412,8 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A396" t="n">
+        <v>2805</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -39489,7 +39467,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N396" s="2" t="n">
+      <c r="N396" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="O396" t="inlineStr">
@@ -39530,6 +39508,412 @@
       <c r="V396" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>106496</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>50</v>
+      </c>
+      <c r="J397" t="n">
+        <v>4</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>43006</v>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>108282</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PROYECTOS PARA EL CAMBIO CLIMÁTICO</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>24</v>
+      </c>
+      <c r="J398" t="n">
+        <v>2</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L398" t="n">
+        <v>20888400</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>43705</v>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LA GRAN COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>101874</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO PÚBLICO</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>44</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2</v>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L399" t="n">
+        <v>22049336</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N399" s="2" t="n">
+        <v>45054</v>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>10123</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO CONSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>32</v>
+      </c>
+      <c r="J400" t="n">
+        <v>2</v>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L400" t="n">
+        <v>7575600</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>36577</v>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V400"/>
+  <dimension ref="A1:V420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39512,10 +39512,8 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A397" t="n">
+        <v>1722</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -39567,7 +39565,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N397" s="2" t="n">
+      <c r="N397" s="1" t="n">
         <v>43006</v>
       </c>
       <c r="O397" t="inlineStr">
@@ -39612,10 +39610,8 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A398" t="n">
+        <v>1728</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -39669,7 +39665,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N398" s="2" t="n">
+      <c r="N398" s="1" t="n">
         <v>43705</v>
       </c>
       <c r="O398" t="inlineStr">
@@ -39714,10 +39710,8 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="A399" t="n">
+        <v>1802</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -39771,7 +39765,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N399" s="2" t="n">
+      <c r="N399" s="1" t="n">
         <v>45054</v>
       </c>
       <c r="O399" t="inlineStr">
@@ -39816,10 +39810,8 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
+      <c r="A400" t="n">
+        <v>1808</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -39873,7 +39865,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N400" s="2" t="n">
+      <c r="N400" s="1" t="n">
         <v>36577</v>
       </c>
       <c r="O400" t="inlineStr">
@@ -39914,6 +39906,2020 @@
       <c r="V400" t="inlineStr">
         <is>
           <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>103217</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CALIDAD EN SALUD</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>26</v>
+      </c>
+      <c r="J401" t="n">
+        <v>2</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>41748</v>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>7740</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN PROMOCION EN SALUD Y DESARROLLO HUMANO</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>24</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2</v>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>36189</v>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>119136</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TERAPIA MANUAL ORTOPÉDICA</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>27</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2</v>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>45044</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>4468</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DE LA CALIDAD</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>30</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2</v>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>44204</v>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>107987</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>30</v>
+      </c>
+      <c r="J405" t="n">
+        <v>2</v>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>43592</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>4927</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN LOGISTICA DEL TRANSPORTE INTERNACIONAL DE MERCANCIAS</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>30</v>
+      </c>
+      <c r="J406" t="n">
+        <v>2</v>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L406" t="n">
+        <v>23557464</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>11504</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN LOGISTICA EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>30</v>
+      </c>
+      <c r="J407" t="n">
+        <v>2</v>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L407" t="n">
+        <v>18638884</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>43816</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>109020</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>48</v>
+      </c>
+      <c r="J408" t="n">
+        <v>4</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L408" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>105481</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO DE LOS NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>19</v>
+      </c>
+      <c r="J409" t="n">
+        <v>3</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>42479</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>103101</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DESARROLLO DE VIDEOJUEGOS</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>16</v>
+      </c>
+      <c r="J410" t="n">
+        <v>3</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>41693</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>11844</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ECONOMIA</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>22</v>
+      </c>
+      <c r="J411" t="n">
+        <v>2</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>37011</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>105120</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>22</v>
+      </c>
+      <c r="J412" t="n">
+        <v>2</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>42331</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>103397</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE PROYECTOS EN SALUD</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>22</v>
+      </c>
+      <c r="J413" t="n">
+        <v>2</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>41822</v>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>54523</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTION DE RIESGO Y CONTROL DE INSTITUCIONES FINANCIERAS</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>20</v>
+      </c>
+      <c r="J414" t="n">
+        <v>5</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Bimensual</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>39902</v>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>105584</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN EDUCACION</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>36</v>
+      </c>
+      <c r="J415" t="n">
+        <v>4</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>42530</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>107632</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN REGULACION</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>36</v>
+      </c>
+      <c r="J416" t="n">
+        <v>3</v>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>43517</v>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>106492</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>MAESTRIA INTERNACIONAL EN FINANZAS</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>35</v>
+      </c>
+      <c r="J417" t="n">
+        <v>14</v>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="L417" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>43016</v>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>115910</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>36</v>
+      </c>
+      <c r="J418" t="n">
+        <v>3</v>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L418" t="n">
+        <v>8231209</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>43704</v>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>102173</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>36</v>
+      </c>
+      <c r="J419" t="n">
+        <v>3</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L419" t="n">
+        <v>8968294</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>43704</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE BOLIVAR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>20244</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN LOGÍSTICA Y CADENA DE SUMINISTRO</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>24</v>
+      </c>
+      <c r="J420" t="n">
+        <v>2</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L420" t="n">
+        <v>9800405</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V420"/>
+  <dimension ref="A1:V434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39910,10 +39910,8 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A401" t="n">
+        <v>1121</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -39965,7 +39963,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N401" s="2" t="n">
+      <c r="N401" s="1" t="n">
         <v>41748</v>
       </c>
       <c r="O401" t="inlineStr">
@@ -40010,10 +40008,8 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A402" t="n">
+        <v>1121</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -40065,7 +40061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N402" s="2" t="n">
+      <c r="N402" s="1" t="n">
         <v>36189</v>
       </c>
       <c r="O402" t="inlineStr">
@@ -40110,10 +40106,8 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A403" t="n">
+        <v>1711</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -40165,7 +40159,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N403" s="2" t="n">
+      <c r="N403" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="O403" t="inlineStr">
@@ -40210,10 +40204,8 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A404" t="n">
+        <v>1713</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -40265,7 +40257,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N404" s="2" t="n">
+      <c r="N404" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="O404" t="inlineStr">
@@ -40310,10 +40302,8 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A405" t="n">
+        <v>1713</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -40365,7 +40355,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N405" s="2" t="n">
+      <c r="N405" s="1" t="n">
         <v>43592</v>
       </c>
       <c r="O405" t="inlineStr">
@@ -40410,10 +40400,8 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A406" t="n">
+        <v>1713</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -40467,7 +40455,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N406" s="2" t="n">
+      <c r="N406" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O406" t="inlineStr">
@@ -40512,10 +40500,8 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A407" t="n">
+        <v>1713</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -40569,7 +40555,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N407" s="2" t="n">
+      <c r="N407" s="1" t="n">
         <v>43816</v>
       </c>
       <c r="O407" t="inlineStr">
@@ -40614,10 +40600,8 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A408" t="n">
+        <v>1732</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -40671,7 +40655,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N408" s="2" t="n">
+      <c r="N408" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O408" t="inlineStr">
@@ -40716,10 +40700,8 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A409" t="n">
+        <v>1813</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -40771,7 +40753,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N409" s="2" t="n">
+      <c r="N409" s="1" t="n">
         <v>42479</v>
       </c>
       <c r="O409" t="inlineStr">
@@ -40816,10 +40798,8 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A410" t="n">
+        <v>1813</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -40871,7 +40851,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N410" s="2" t="n">
+      <c r="N410" s="1" t="n">
         <v>41693</v>
       </c>
       <c r="O410" t="inlineStr">
@@ -40916,10 +40896,8 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A411" t="n">
+        <v>1813</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -40971,7 +40949,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N411" s="2" t="n">
+      <c r="N411" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="O411" t="inlineStr">
@@ -41016,10 +40994,8 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A412" t="n">
+        <v>1813</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -41071,7 +41047,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N412" s="2" t="n">
+      <c r="N412" s="1" t="n">
         <v>42331</v>
       </c>
       <c r="O412" t="inlineStr">
@@ -41116,10 +41092,8 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A413" t="n">
+        <v>1813</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -41171,7 +41145,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N413" s="2" t="n">
+      <c r="N413" s="1" t="n">
         <v>41822</v>
       </c>
       <c r="O413" t="inlineStr">
@@ -41216,10 +41190,8 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A414" t="n">
+        <v>1813</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -41271,7 +41243,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N414" s="2" t="n">
+      <c r="N414" s="1" t="n">
         <v>39902</v>
       </c>
       <c r="O414" t="inlineStr">
@@ -41316,10 +41288,8 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A415" t="n">
+        <v>1813</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -41371,7 +41341,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N415" s="2" t="n">
+      <c r="N415" s="1" t="n">
         <v>42530</v>
       </c>
       <c r="O415" t="inlineStr">
@@ -41416,10 +41386,8 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A416" t="n">
+        <v>1813</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -41471,7 +41439,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N416" s="2" t="n">
+      <c r="N416" s="1" t="n">
         <v>43517</v>
       </c>
       <c r="O416" t="inlineStr">
@@ -41516,10 +41484,8 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A417" t="n">
+        <v>1813</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -41573,7 +41539,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N417" s="2" t="n">
+      <c r="N417" s="1" t="n">
         <v>43016</v>
       </c>
       <c r="O417" t="inlineStr">
@@ -41618,10 +41584,8 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A418" t="n">
+        <v>1823</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -41675,7 +41639,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N418" s="2" t="n">
+      <c r="N418" s="1" t="n">
         <v>43704</v>
       </c>
       <c r="O418" t="inlineStr">
@@ -41720,10 +41684,8 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A419" t="n">
+        <v>1823</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -41777,7 +41739,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N419" s="2" t="n">
+      <c r="N419" s="1" t="n">
         <v>43704</v>
       </c>
       <c r="O419" t="inlineStr">
@@ -41822,10 +41784,8 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
+      <c r="A420" t="n">
+        <v>1832</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -41879,7 +41839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N420" s="2" t="n">
+      <c r="N420" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O420" t="inlineStr">
@@ -41920,6 +41880,1412 @@
       <c r="V420" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LLANOS</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>3586</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ACUICULTURA - AGUAS CONTINENTALES</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>26</v>
+      </c>
+      <c r="J421" t="n">
+        <v>2</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L421" t="n">
+        <v>5462824</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Pesca</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Pesca</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>Zootecnia</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DE CONSTRUCCIONES</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>26</v>
+      </c>
+      <c r="J422" t="n">
+        <v>2</v>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>106149</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>56</v>
+      </c>
+      <c r="J423" t="n">
+        <v>4</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>42801</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>106147</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DESARROLLO DE PROCESOS COMUNICATIVOS EN EDUCACIÓN: LECTO-ESCRITURA</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>50</v>
+      </c>
+      <c r="J424" t="n">
+        <v>4</v>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>42801</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>91074</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN PEDAGOGIA DE LAS TECNOLOGIAS DE LA INFORMACION Y LA COMUNICACION</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>45</v>
+      </c>
+      <c r="J425" t="n">
+        <v>4</v>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>40605</v>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>102088</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ACTIVIDAD FÍSICA PARA LA SALUD</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>54</v>
+      </c>
+      <c r="J426" t="n">
+        <v>4</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L426" t="n">
+        <v>8684855</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>41254</v>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>107548</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DIRECCIÓN PORTUARIA Y MARÍTIMA</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>42</v>
+      </c>
+      <c r="J427" t="n">
+        <v>4</v>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>43412</v>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>53599</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PSICOTERAPIA Y CONSULTORÍA SISTÉMICA</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>26</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2</v>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>39553</v>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>101549</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INFORMÁTICA Y TELECOMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+      <c r="J429" t="n">
+        <v>4</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>40942</v>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD FUCS</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>108439</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MERCADEO EN SALUD</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>28</v>
+      </c>
+      <c r="J430" t="n">
+        <v>2</v>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L430" t="n">
+        <v>7424725</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>Publicidad y afines</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>105331</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ALTA GERENCIA</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>28</v>
+      </c>
+      <c r="J431" t="n">
+        <v>2</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>42416</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>8088</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DE INSTITUCIONES DE SALUD</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>27</v>
+      </c>
+      <c r="J432" t="n">
+        <v>2</v>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>36262</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>105302</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>28</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>42412</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>102597</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN REVISORÍA FISCAL Y AUDITORÍA FORENSE</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>27</v>
+      </c>
+      <c r="J434" t="n">
+        <v>2</v>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>41459</v>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>
